--- a/template.xlsx
+++ b/template.xlsx
@@ -721,7 +721,7 @@
       <formula1>_lists!$C$2:$C$5</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>_lists!$D$2:$D$9</formula1>
+      <formula1>_lists!$D$2:$D$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -892,6 +892,11 @@
           <t>ASK_PRODUCT</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pv-4fe13ab2-5809-4b6c-9feb-f830010ed760</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -899,6 +904,11 @@
           <t>ASK_MATERIAL</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pv-fdb7a34a-243d-42f2-bbcb-cb78cfd027fa</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -906,6 +916,11 @@
           <t>ASK_SIZE_FIT</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pv-a7e16e7d-81e3-45a7-803c-72e22c7dbdc6</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -913,11 +928,21 @@
           <t>ASK_EXPIRY</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>pv-07ea9d28-97d6-49c9-9d60-7d48dc03d4c9</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
           <t>ASK_CHILDREN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pv-9518481c-4d54-445d-a5d7-3db2b4114a0a</t>
         </is>
       </c>
     </row>
